--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6809C_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6809C_SW2.xlsx
@@ -1005,7 +1005,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>Air-Way FF6809 (s27, double-pass 2026-10-15, parts.air-way.com/api/series/27, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p11 FS6809-20-20-NWO-FG (ORFS-p011-t01); FORGED part: Air-Way NON-forged row FF6809-20-20 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6809 (s27, double-pass 2026-10-15, parts.air-way.com/api/series/27, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p11 FS6809-20-20-NWO-FG (ORFS-p011-t01); FORGED part: Air-Way NON-forged row FF6809-20-20 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
